--- a/tests/workbooktests/workbooks/test_bonds.xlsx
+++ b/tests/workbooktests/workbooks/test_bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EB2479-D6F1-4F10-B427-76F9075469C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B264A8AF-0439-47A0-AB71-C5E9EC1F6793}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B14" s="29" t="str">
         <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13,,,B2)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R14C2Schedule,H</v>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R14C2Schedule,A</v>
       </c>
       <c r="C14" s="30" t="str">
         <f>_xll.qlSchedule(C6,C7,C8,C9,C10,C11,C12,C13,,,C2)</f>
@@ -2045,11 +2045,11 @@
         <v>110</v>
       </c>
       <c r="B24" s="36" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly",,B14)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R24C2YieldTermStructureHandle,H</v>
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly",B14)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R24C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C24" s="37" t="str">
-        <f>_xll.qlFlatForward(C2,0.03,"Actual360","Compounded","Quarterly",,C14)</f>
+        <f>_xll.qlFlatForward(C2,0.03,"Actual360","Compounded","Quarterly",C14)</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R24C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C36" s="30" t="str">
         <f>_xll.qlCmsRateBond(C4,C5,C14,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34,C35,C25)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R36C3CmsRateBond,H</v>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R36C3CmsRateBond,A</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2396,11 +2396,11 @@
         <v>55</v>
       </c>
       <c r="B53" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B36)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B36)</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R53C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,C36)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",C36)</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R53C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>154</v>
       </c>
       <c r="B68" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B36)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B36)</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R68C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C68" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C36)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C36)</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R68C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B16" s="29" t="str">
         <f>_xll.qlSchedule(B8,B9,B10,B11,B12,B13,B14,B15,,,B2)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R16C2Schedule,H</v>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R16C2Schedule,A</v>
       </c>
       <c r="C16" s="30" t="str">
         <f>_xll.qlSchedule(C8,C9,C10,C11,C12,C13,C14,C15,,,C2)</f>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B25" s="36" t="str">
         <f>_xll.qlEuribor("3M",,B16)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R25C2Euribor,G</v>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R25C2Euribor,A</v>
       </c>
       <c r="C25" s="37" t="str">
         <f>_xll.qlEuribor("3M",,C16)</f>
@@ -2945,11 +2945,11 @@
         <v>110</v>
       </c>
       <c r="B26" s="36" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly",,B25)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C2YieldTermStructureHandle,H</v>
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly",B25)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C26" s="37" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly",,C25)</f>
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly",C25)</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B27" s="29" t="str">
         <f>_xll.qlSwapIndex(B17,B18,B19,B20,B21,B22,B23,B24,B25,B26,B26)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R27C2SwapIndex,H</v>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R27C2SwapIndex,A</v>
       </c>
       <c r="C27" s="30" t="str">
         <f>_xll.qlSwapIndex(C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C26)</f>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B37" s="117" t="str">
         <f>_xll.qlAmortizingCmsRateBond(B4,B5:B7,B16,B27,B28,,,,,,,,,B27)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R37C2AmortizingCmsRateBond,H</v>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R37C2AmortizingCmsRateBond,A</v>
       </c>
       <c r="C37" s="118" t="str">
         <f>_xll.qlAmortizingCmsRateBond(C4,C5:C7,C16,C27,C28,C29,C30,C31,C32,C33,C34,C35,C36,C27)</f>
@@ -3275,11 +3275,11 @@
         <v>55</v>
       </c>
       <c r="B54" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B37)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B37)</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C54" s="20" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,C37)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",C37)</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3466,11 +3466,11 @@
         <v>154</v>
       </c>
       <c r="B69" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B37)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B37)</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R69C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C69" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C37)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C37)</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R69C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B7" s="54" t="str">
         <f>_xll.qlCallabilityPrice(B6,B6)</f>
-        <v>欣[test_bonds.xlsx]Callability!R7C2BondPrice,G</v>
+        <v>欣[test_bonds.xlsx]Callability!R7C2BondPrice,A</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B15" s="54" t="str">
         <f>_xll.qlCallabilityPrice(B14,B14)</f>
-        <v>欣[test_bonds.xlsx]Callability!R15C2BondPrice,G</v>
+        <v>欣[test_bonds.xlsx]Callability!R15C2BondPrice,A</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -4235,11 +4235,11 @@
         <v>110</v>
       </c>
       <c r="B48" s="22" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360",,,,B30)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360",,,B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C48" s="23" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360",,,,C30)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360",,,C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -4452,11 +4452,11 @@
         <v>154</v>
       </c>
       <c r="B65" s="22" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B64)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B64)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R65C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C65" s="23" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C64)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C64)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R65C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -4574,11 +4574,11 @@
         <v>154</v>
       </c>
       <c r="B75" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B74)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B74)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R75C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C75" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C74)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C74)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R75C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -4669,11 +4669,11 @@
         <v>172</v>
       </c>
       <c r="B84" s="22" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,,B83)</f>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B83)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R84C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C84" s="23" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+      <c r="C84" s="22" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,C83)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R84C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -4780,11 +4780,11 @@
         <v>172</v>
       </c>
       <c r="B93" s="22" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,,B92)</f>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B92)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R93C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C93" s="23" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,,C92)</f>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,C92)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R93C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -5862,11 +5862,11 @@
         <v>110</v>
       </c>
       <c r="B34" s="22" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly",,B16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C2YieldTermStructureHandle,H</v>
-      </c>
-      <c r="C34" s="23" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly",B16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C34" s="22" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly",C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B43" s="46" t="str">
         <f>_xll.qlBondPrice(B37,"clean",B36)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C2BondPrice,I</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C2BondPrice,A</v>
       </c>
       <c r="C43" s="47" t="str">
         <f>_xll.qlBondPrice(C37,"clean")</f>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B49" s="22" t="str">
         <f>_xll.qlCallableBondCallability(B16,B16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C2Callability,I</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C2Callability,A</v>
       </c>
       <c r="C49" s="23" t="str">
         <f>_xll.qlCallableBondCallability(C16)</f>
@@ -6092,11 +6092,11 @@
         <v>154</v>
       </c>
       <c r="B52" s="22" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B51)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C2YieldTermStructureHandle,H</v>
-      </c>
-      <c r="C52" s="23" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B51)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C52" s="22" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C51)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -6214,11 +6214,11 @@
         <v>154</v>
       </c>
       <c r="B62" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B61)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C2YieldTermStructureHandle,H</v>
-      </c>
-      <c r="C62" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B61)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C62" s="46" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C61)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -6309,11 +6309,11 @@
         <v>172</v>
       </c>
       <c r="B71" s="22" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,,B70)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R71C2YieldTermStructureHandle,H</v>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B70)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R71C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C71" s="23" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,,C70)</f>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,C70)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R71C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="B74" s="22" t="str">
         <f>_xll.qlHullWhite(B71,B72,B73,B71)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R74C2HullWhite,G</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R74C2HullWhite,A</v>
       </c>
       <c r="C74" s="23" t="str">
         <f>_xll.qlHullWhite(C71,C72,C73,C71)</f>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="B76" s="22" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine(B74,B75,,B74)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R76C2TreeCallableFixedRateBondEngine,G</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R76C2TreeCallableFixedRateBondEngine,A</v>
       </c>
       <c r="C76" s="23" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine(C74,C75,,C74)</f>
@@ -6420,11 +6420,11 @@
         <v>172</v>
       </c>
       <c r="B80" s="22" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,,B79)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R80C2YieldTermStructureHandle,H</v>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B79)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R80C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C80" s="23" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,,C79)</f>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,C79)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R80C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B83" s="22" t="str">
         <f>_xll.qlHullWhite(B80,B81,B82,B80)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R83C2HullWhite,G</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R83C2HullWhite,A</v>
       </c>
       <c r="C83" s="23" t="str">
         <f>_xll.qlHullWhite(C80,C81,C82,C80)</f>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="B84" s="22" t="str">
         <f>_xll.qlTimeGridFromTimes(B91:B206,B83)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R84C2TimeGrid,G</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R84C2TimeGrid,A</v>
       </c>
       <c r="C84" s="23" t="str">
         <f>_xll.qlTimeGridFromTimes(B91:B206,C83)</f>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="B85" s="22" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine2(B83,B84,,B84)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R85C2TreeCallableFixedRateBondEngine,G</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R85C2TreeCallableFixedRateBondEngine,A</v>
       </c>
       <c r="C85" s="23" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine2(C83,C84,,C84)</f>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="B10" s="22" t="str">
         <f>_xll.qlCustomRegion("TestRegion","TR",B2)</f>
-        <v>欣[test_bonds.xlsx]CPIBond!R10C2CustomRegion,G</v>
+        <v>欣[test_bonds.xlsx]CPIBond!R10C2CustomRegion,A</v>
       </c>
       <c r="C10" s="23" t="str">
         <f>_xll.qlCustomRegion("TestRegion","TR",C2)</f>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="B19" s="29" t="str">
         <f>_xll.qlZeroInflationCurve($B$1,B15:B16,B17:B18,"Annual","Actual365fixed",,B10)</f>
-        <v>欣[test_bonds.xlsx]CPIBond!R19C2ZeroInflationTermStructureHandle,H</v>
+        <v>欣[test_bonds.xlsx]CPIBond!R19C2ZeroInflationTermStructureHandle,A</v>
       </c>
       <c r="C19" s="30" t="str">
         <f>_xll.qlZeroInflationCurve($B$1,C15:C16,C17:C18,"Annual","Actual365fixed",,C10)</f>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="B20" s="29" t="str">
         <f>_xll.qlZeroInflationIndex(B9,B10,B11,B12,B13,B14,B19,B19)</f>
-        <v>欣[test_bonds.xlsx]CPIBond!R20C2ZeroInflationIndex,H</v>
+        <v>欣[test_bonds.xlsx]CPIBond!R20C2ZeroInflationIndex,A</v>
       </c>
       <c r="C20" s="30" t="str">
         <f>_xll.qlZeroInflationIndex(C9,C10,C11,C12,C13,C14,C19,C19)</f>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B33" s="29" t="str">
         <f>_xll.qlSchedule(B25,B26,B27,B28,B29,B30,B31,B32,,,B23)</f>
-        <v>欣[test_bonds.xlsx]CPIBond!R33C2Schedule,H</v>
+        <v>欣[test_bonds.xlsx]CPIBond!R33C2Schedule,A</v>
       </c>
       <c r="C33" s="30" t="str">
         <f>_xll.qlSchedule(C25,C26,C27,C28,C29,C30,C31,C32,,,C23)</f>
@@ -7785,11 +7785,11 @@
         <v>55</v>
       </c>
       <c r="B60" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B43)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B43)</f>
         <v>欣[test_bonds.xlsx]CPIBond!R60C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,C43)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",C43)</f>
         <v>欣[test_bonds.xlsx]CPIBond!R60C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -7976,11 +7976,11 @@
         <v>154</v>
       </c>
       <c r="B75" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B43)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B43)</f>
         <v>欣[test_bonds.xlsx]CPIBond!R75C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C75" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C43)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C43)</f>
         <v>欣[test_bonds.xlsx]CPIBond!R75C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="B10" s="102" t="str">
         <f>_xll.qlMakeSchedule(B5,B6, "12M","annual",B4,B8,B8,"Forward",0,,,,,B2)</f>
-        <v>欣[test_bonds.xlsx]Bond!R10C2Schedule,H</v>
+        <v>欣[test_bonds.xlsx]Bond!R10C2Schedule,A</v>
       </c>
       <c r="C10" s="103"/>
     </row>
@@ -8450,11 +8450,11 @@
         <v>50</v>
       </c>
       <c r="B23" s="22" t="str">
-        <f>_xll.qlFixedRateLeg(B10,B9,B11:B18,C11:C12,,B10)</f>
+        <f>_xll.qlFixedRateLeg(B10,B9,B11:B18,C11:C12,,,,,,,,,,,,B10)</f>
         <v>欣[test_bonds.xlsx]Bond!R23C2CashFlow,A</v>
       </c>
-      <c r="C23" s="23" t="str">
-        <f>_xll.qlFixedRateLeg(B10,B9,B11:B18,C11:C12,,B10)</f>
+      <c r="C23" s="22" t="str">
+        <f>_xll.qlFixedRateLeg(B10,B9,B11:B18,C11:C12,,,,,,,,,,,,B10)</f>
         <v>欣[test_bonds.xlsx]Bond!R23C3CashFlow,A</v>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C25" s="30" t="str">
         <f>_xll.qlBond(C19,C20,C21,C22,C23,C24,C23)</f>
-        <v>欣[test_bonds.xlsx]Bond!R25C3Bond,H</v>
+        <v>欣[test_bonds.xlsx]Bond!R25C3Bond,A</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -8605,7 +8605,7 @@
         <f>_xll.qlBondIssueDate(B25,B25)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="68">
+      <c r="C35" s="87">
         <f>_xll.qlBondIssueDate(C25,C25)</f>
         <v>45663</v>
       </c>
@@ -8693,11 +8693,11 @@
         <v>55</v>
       </c>
       <c r="B42" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B25)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B25)</f>
         <v>欣[test_bonds.xlsx]Bond!R42C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C42" s="20" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,C25)</f>
+      <c r="C42" s="19" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",C25)</f>
         <v>欣[test_bonds.xlsx]Bond!R42C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -8991,11 +8991,11 @@
       </c>
       <c r="B11" s="29" t="str">
         <f>_xll.qlZeroCouponBond(B4,B5,B6,B7,,,,B2)</f>
-        <v>欣[test_bonds.xlsx]ZeroCouponBond!R11C2ZeroCouponBond,H</v>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R11C2ZeroCouponBond,A</v>
       </c>
       <c r="C11" s="30" t="str">
         <f>_xll.qlZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,B2)</f>
-        <v>欣[test_bonds.xlsx]ZeroCouponBond!R11C3ZeroCouponBond,H</v>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R11C3ZeroCouponBond,A</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -9211,11 +9211,11 @@
         <v>55</v>
       </c>
       <c r="B28" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B11)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B11)</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R28C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C28" s="20" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual",B2)</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R28C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       <c r="A29" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="22" t="str">
+      <c r="B29" s="29" t="str">
         <f>_xll.qlDiscountingBondEngine(B28,B28)</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R29C2DiscountingBondEngine,A</v>
       </c>
@@ -9233,14 +9233,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="25" t="s">
         <v>152</v>
       </c>
       <c r="B30" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B11,B29,B29)</f>
         <v>1</v>
       </c>
-      <c r="C30" s="20" t="b">
+      <c r="C30" s="23" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C11,C29)</f>
         <v>1</v>
       </c>
@@ -9402,11 +9402,11 @@
         <v>154</v>
       </c>
       <c r="B43" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B11)</f>
-        <v>欣[test_bonds.xlsx]ZeroCouponBond!R43C2YieldTermStructureHandle,H</v>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B11)</f>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R43C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C43" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C11)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C11)</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R43C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="B14" s="29" t="str">
         <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13,,,B2)</f>
-        <v>欣[test_bonds.xlsx]FixedRateBond!R14C2Schedule,H</v>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R14C2Schedule,A</v>
       </c>
       <c r="C14" s="30" t="str">
         <f>_xll.qlSchedule(C6,C7,C8,C9,C10,C11,C12,C13,,,C2)</f>
@@ -9750,11 +9750,11 @@
       </c>
       <c r="B27" s="29" t="str">
         <f>_xll.qlFixedRateBond(B4,B5,B14,B15:B17,B18,,,,,,,,,B14)</f>
-        <v>欣[test_bonds.xlsx]FixedRateBond!R27C2FixedRateBond,H</v>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R27C2FixedRateBond,A</v>
       </c>
       <c r="C27" s="30" t="str">
         <f>_xll.qlFixedRateBond(C4,C5,C14,C15:C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C14)</f>
-        <v>欣[test_bonds.xlsx]FixedRateBond!R27C3FixedRateBond,H</v>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R27C3FixedRateBond,A</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -9970,11 +9970,11 @@
         <v>55</v>
       </c>
       <c r="B44" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B27)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B27)</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R44C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C44" s="20" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,C27)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",C27)</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R44C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -10161,11 +10161,11 @@
         <v>154</v>
       </c>
       <c r="B59" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B27)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B27)</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R59C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C59" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C27)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C27)</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R59C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -10751,11 +10751,11 @@
         <v>55</v>
       </c>
       <c r="B47" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B30)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B30)</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R47C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,C30)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",C30)</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R47C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -10912,20 +10912,20 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
+      <c r="A60" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="B60" s="61">
+      <c r="B60" s="51">
         <f>_xll.qlBondSettlementValue(B30,B49)</f>
         <v>175.29814998167899</v>
       </c>
-      <c r="C60" s="62">
+      <c r="C60" s="52">
         <f>_xll.qlBondSettlementValue(C30,C49)</f>
         <v>187.26946093513047</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="50" t="s">
         <v>41</v>
       </c>
       <c r="B61" s="51">
@@ -10941,12 +10941,12 @@
       <c r="A62" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B62" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B30)</f>
+      <c r="B62" s="61" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B30)</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R62C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C62" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C30)</f>
+      <c r="C62" s="62" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C30)</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R62C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -11197,11 +11197,11 @@
         <v>55</v>
       </c>
       <c r="B17" s="111" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly",,B16)</f>
-        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C2YieldTermStructureHandle,H</v>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly",B16)</f>
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C17" s="112" t="str">
-        <f>_xll.qlFlatForward(C2,0.03,"actual360","compounded","Quarterly",,C16)</f>
+        <f>_xll.qlFlatForward(C2,0.03,"actual360","compounded","Quarterly",C16)</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B18" s="29" t="str">
         <f>_xll.qlEuribor("3M",B17,B17)</f>
-        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R18C2Euribor,G</v>
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R18C2Euribor,A</v>
       </c>
       <c r="C18" s="30" t="str">
         <f>_xll.qlEuribor("3M",C17,C17)</f>
@@ -11578,11 +11578,11 @@
         <v>55</v>
       </c>
       <c r="B51" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B34)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B34)</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R51C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,C34)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",C34)</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R51C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -11769,11 +11769,11 @@
         <v>154</v>
       </c>
       <c r="B66" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B34)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B34)</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R66C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C66" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C34)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C34)</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R66C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -12387,11 +12387,11 @@
         <v>55</v>
       </c>
       <c r="B49" s="19" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,B32)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",B32)</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R49C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",,C32)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual360","compounded","Annual",C32)</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R49C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -12578,11 +12578,11 @@
         <v>154</v>
       </c>
       <c r="B64" s="46" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,B32)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B32)</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R64C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C64" s="47" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,,C32)</f>
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,C32)</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R64C3YieldTermStructureHandle,A</v>
       </c>
     </row>

--- a/tests/workbooktests/workbooks/test_bonds.xlsx
+++ b/tests/workbooktests/workbooks/test_bonds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B264A8AF-0439-47A0-AB71-C5E9EC1F6793}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79712706-A415-425D-AD99-9E72E8874A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -42,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="212">
   <si>
     <t>Bond</t>
   </si>
@@ -444,9 +455,6 @@
   </si>
   <si>
     <t>put_call_schedule</t>
-  </si>
-  <si>
-    <t>act/360</t>
   </si>
   <si>
     <t xml:space="preserve">date </t>
@@ -1310,9 +1318,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1350,7 +1358,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1456,7 +1464,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1598,7 +1606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1649,7 +1657,7 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -2071,10 +2079,10 @@
         <v>67</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2406,7 +2414,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B54" s="22" t="str">
         <f>_xll.qlDiscountingBondEngine(B53,B53)</f>
@@ -2419,7 +2427,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B55" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B36,B54,B54)</f>
@@ -2499,11 +2507,11 @@
       </c>
       <c r="B61" s="61">
         <f>_xll.qlBondYield(B36,"actual360","CONTINUOUS","annual",,,B55)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544471E-2</v>
       </c>
       <c r="C61" s="62">
         <f>_xll.qlBondYield(C36,"actual360","CONTINUOUS","annual",,,C55)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544432E-2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2525,11 +2533,11 @@
       </c>
       <c r="B63" s="48">
         <f>_xll.qlBondYield2(B36,B62,"actual360","CONTINUOUS","annual",,,,,B62)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544471E-2</v>
       </c>
       <c r="C63" s="49">
         <f>_xll.qlBondYield2(C36,C62,"actual360","CONTINUOUS","annual",,,,,C62)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544432E-2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2584,7 +2592,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B68" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B36)</f>
@@ -2597,7 +2605,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B69" s="61">
         <v>5.0000000000000001E-3</v>
@@ -2608,47 +2616,47 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C70" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B71" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C71" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B72" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C72" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B73" s="61"/>
       <c r="C73" s="62"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B74" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B36,B68,B69,B70,B71,B72,,B68)</f>
@@ -2761,10 +2769,10 @@
         <v>46</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2921,10 +2929,10 @@
         <v>107</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2971,10 +2979,10 @@
         <v>67</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -3285,7 +3293,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B55" s="22" t="str">
         <f>_xll.qlDiscountingBondEngine(B54,B54)</f>
@@ -3298,7 +3306,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B56" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B37,B55,B55)</f>
@@ -3378,11 +3386,11 @@
       </c>
       <c r="B62" s="61">
         <f>_xll.qlBondYield(B37,"actual360","CONTINUOUS","annual",,,B56)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544436E-2</v>
       </c>
       <c r="C62" s="62">
         <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual",,,C56)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544401E-2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3404,11 +3412,11 @@
       </c>
       <c r="B64" s="48">
         <f>_xll.qlBondYield2(B37,B63,"actual360","CONTINUOUS","annual",,,,,B63)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544436E-2</v>
       </c>
       <c r="C64" s="49">
         <f>_xll.qlBondYield2(C37,C63,"actual360","CONTINUOUS","annual",,,,,C63)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544401E-2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3463,7 +3471,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B69" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B37)</f>
@@ -3476,7 +3484,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B70" s="61">
         <v>5.0000000000000001E-3</v>
@@ -3487,47 +3495,47 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B71" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B72" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B73" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C73" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B74" s="61"/>
       <c r="C74" s="62"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B75" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B37,B69,B70,B71,B72,B73,,B56)</f>
@@ -3636,7 +3644,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B13" s="23">
         <v>4.4999999999999998E-2</v>
@@ -3644,7 +3652,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B14" s="30" t="str">
         <f>_xll.qlSoftCallability(B11,B12,B13)</f>
@@ -3759,10 +3767,10 @@
         <v>46</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3805,10 +3813,10 @@
         <v>77</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -3839,8 +3847,8 @@
       <c r="A15" s="121" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="22">
-        <v>0.05</v>
+      <c r="B15" s="23">
+        <v>0.03</v>
       </c>
       <c r="C15" s="23">
         <v>0.03</v>
@@ -3848,8 +3856,8 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="121"/>
-      <c r="B16" s="22">
-        <v>0.05</v>
+      <c r="B16" s="23">
+        <v>0.03</v>
       </c>
       <c r="C16" s="23">
         <v>0.03</v>
@@ -3857,8 +3865,8 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="121"/>
-      <c r="B17" s="22">
-        <v>0.05</v>
+      <c r="B17" s="23">
+        <v>0.03</v>
       </c>
       <c r="C17" s="23">
         <v>0.03</v>
@@ -3869,10 +3877,10 @@
         <v>83</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -3926,15 +3934,15 @@
         <v>126</v>
       </c>
       <c r="B23" s="41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B24" s="41">
         <v>46754</v>
@@ -4000,7 +4008,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="69" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B30" s="67" t="str">
         <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25,,,,,B25)</f>
@@ -4017,7 +4025,7 @@
       </c>
       <c r="B31" s="19">
         <f>_xll.qlBondNextCouponRate(B30,,B30)</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="C31" s="20">
         <f>_xll.qlBondNextCouponRate(C30,,C30)</f>
@@ -4221,7 +4229,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B47" s="19">
         <v>0.2</v>
@@ -4245,7 +4253,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B49" s="29" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(B47,B48,B48)</f>
@@ -4258,7 +4266,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B50" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B30,B49)</f>
@@ -4275,11 +4283,11 @@
       </c>
       <c r="B51" s="70">
         <f>_xll.qlBondCleanPrice(B30,B50)</f>
-        <v>107.51781078466064</v>
+        <v>99.411363118905641</v>
       </c>
       <c r="C51" s="71">
         <f>_xll.qlBondCleanPrice(C30,C50)</f>
-        <v>99.448292731770522</v>
+        <v>99.401463373482386</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -4299,11 +4307,11 @@
       </c>
       <c r="B53" s="48">
         <f>_xll.qlBondCleanPrice2(B30,B52,"actual360","continuous",,,B50)</f>
-        <v>112.82281423407628</v>
+        <v>100.27732450208939</v>
       </c>
       <c r="C53" s="49">
         <f>_xll.qlBondCleanPrice2(C30,C52,"actual360","continuous",,,C50)</f>
-        <v>100.54551097389133</v>
+        <v>100.27732450208939</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -4312,11 +4320,11 @@
       </c>
       <c r="B54" s="61">
         <f>_xll.qlBondDirtyPrice(B30,B50)</f>
-        <v>107.57336634021621</v>
+        <v>99.444696452238972</v>
       </c>
       <c r="C54" s="62">
         <f>_xll.qlBondDirtyPrice(C30,C50)</f>
-        <v>99.481626065103853</v>
+        <v>99.434796706815717</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -4325,11 +4333,11 @@
       </c>
       <c r="B55" s="51">
         <f>_xll.qlBondDirtyPrice2(B30,B52,"actual360","CONTINUOUS","annual",,B50)</f>
-        <v>112.87836978963185</v>
+        <v>100.31065783542272</v>
       </c>
       <c r="C55" s="52">
         <f>_xll.qlBondDirtyPrice2(C30,C52,"actual360","CONTINUOUS","annual",,C50)</f>
-        <v>100.57884430722466</v>
+        <v>100.31065783542272</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -4338,11 +4346,11 @@
       </c>
       <c r="B56" s="61">
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual",,,B50)</f>
-        <v>3.6789469194412242E-2</v>
+        <v>3.0273594634523941E-2</v>
       </c>
       <c r="C56" s="62">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual",,,C50)</f>
-        <v>3.0632255029678354E-2</v>
+        <v>3.0289046398940006E-2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -4364,11 +4372,11 @@
       </c>
       <c r="B58" s="48">
         <f>_xll.qlBondYield2(B30,B57,"actual360","CONTINUOUS","annual",,,,,B57)</f>
-        <v>3.6874035596847536E-2</v>
+        <v>3.0273594634523941E-2</v>
       </c>
       <c r="C58" s="49">
         <f>_xll.qlBondYield2(C30,C57,"actual360","CONTINUOUS","annual",,,,,C57)</f>
-        <v>3.0684329366683964E-2</v>
+        <v>3.0289046398940006E-2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -4388,7 +4396,7 @@
       </c>
       <c r="B60" s="48">
         <f>_xll.qlBondAccruedAmount(B30,B59,B50)</f>
-        <v>0.11111111111110628</v>
+        <v>6.6666666666659324E-2</v>
       </c>
       <c r="C60" s="49">
         <f>_xll.qlBondAccruedAmount(C30,C59,C50)</f>
@@ -4401,11 +4409,11 @@
       </c>
       <c r="B61" s="57">
         <f>_xll.qlBondSettlementValue(B30,B50)</f>
-        <v>107.57336634021623</v>
+        <v>99.444696452238972</v>
       </c>
       <c r="C61" s="57">
         <f>_xll.qlBondSettlementValue(C30,C50)</f>
-        <v>99.481626065103839</v>
+        <v>99.434796706815717</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -4414,16 +4422,16 @@
       </c>
       <c r="B62" s="57">
         <f>_xll.qlBondSettlementValue2(B30,B51)</f>
-        <v>107.57336634021621</v>
+        <v>99.444696452238972</v>
       </c>
       <c r="C62" s="57">
         <f>_xll.qlBondSettlementValue2(C30,C51)</f>
-        <v>99.481626065103853</v>
+        <v>99.434796706815717</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B63" s="59" t="str">
         <f>_xll.qlCallableBondCallability(B30,B30)</f>
@@ -4436,7 +4444,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="45" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B64" s="19" t="str">
         <f>_xll.qlBondPrice(B51,"Clean",B51)</f>
@@ -4449,7 +4457,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B65" s="22" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B64)</f>
@@ -4462,7 +4470,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B66" s="60">
         <v>9.9999999999999995E-7</v>
@@ -4473,7 +4481,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B67" s="22">
         <v>100</v>
@@ -4484,7 +4492,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B68" s="22">
         <v>0.01</v>
@@ -4495,7 +4503,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B69" s="22">
         <v>0.5</v>
@@ -4506,36 +4514,36 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B70" s="65">
         <f>_xll.qlCallableBondImpliedVolatility(B30,B64,B65,B66,B67,B68,B69,B65)</f>
-        <v>0.25214788562896018</v>
+        <v>0.26393116080354267</v>
       </c>
       <c r="C70" s="66">
         <f>_xll.qlCallableBondImpliedVolatility(C30,C64,C65,C66,C67,C68,C69,C65)</f>
-        <v>0.25030192954114117</v>
+        <v>0.26212412019966747</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="96" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B71" s="97">
         <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual",,B50)</f>
-        <v>107.48195897151473</v>
+        <v>99.378220410846438</v>
       </c>
       <c r="C71" s="98">
         <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual",,C50)</f>
-        <v>99.415137715891774</v>
+        <v>99.368323964788402</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B72" s="22">
-        <f>_xll.qlCallableBondOAS(B30,B71,B48,"30/360","compounded","Annual",,,,,B71)</f>
+        <f>_xll.qlCallableBondOAS(B30,B71,B48,"30/360","compounded","Annual",B36,0.0000000001,100,0,B71)</f>
         <v>0</v>
       </c>
       <c r="C72" s="23">
@@ -4545,7 +4553,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B73" s="67">
         <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
@@ -4558,7 +4566,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B74" s="22">
         <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
@@ -4571,7 +4579,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B75" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B74)</f>
@@ -4584,7 +4592,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B76" s="61">
         <v>5.0000000000000001E-3</v>
@@ -4595,55 +4603,55 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B77" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C77" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B78" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C78" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B79" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C79" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B80" s="61"/>
       <c r="C80" s="62"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B81" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B30,B75,B76,B77,B78,B79,,B75)</f>
-        <v>109.12539731768376</v>
+        <v>96.827373159451469</v>
       </c>
       <c r="C81" s="30">
         <f>_xll.qlBondCleanPriceFromZSpread(C30,C75,C76,C77,C78,C79,,C75)</f>
-        <v>97.090069430863338</v>
+        <v>96.827373159451469</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -4653,7 +4661,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B83" s="19" t="str">
         <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25,,,,,B30)</f>
@@ -4666,7 +4674,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B84" s="22" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B83)</f>
@@ -4679,7 +4687,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B85" s="22">
         <v>0.03</v>
@@ -4690,7 +4698,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B86" s="22">
         <v>0.01</v>
@@ -4701,7 +4709,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B87" s="22" t="str">
         <f>_xll.qlHullWhite(B84,B85,B86,B84)</f>
@@ -4714,7 +4722,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B88" s="22">
         <v>100</v>
@@ -4725,7 +4733,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B89" s="22" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine(B87,B88,,B87)</f>
@@ -4738,7 +4746,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B90" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B83,B89,B89)</f>
@@ -4755,16 +4763,16 @@
       </c>
       <c r="B91" s="29">
         <f>_xll.qlBondCleanPrice(B83,B90)</f>
-        <v>110.79757382947662</v>
+        <v>104.61923824416269</v>
       </c>
       <c r="C91" s="30">
         <f>_xll.qlBondCleanPrice(C83,C90)</f>
-        <v>104.15316507210984</v>
+        <v>104.61923824416269</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B92" s="19" t="str">
         <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25,,,,,B30)</f>
@@ -4777,7 +4785,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B93" s="22" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B92)</f>
@@ -4790,7 +4798,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B94" s="22">
         <v>0.03</v>
@@ -4801,7 +4809,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B95" s="22">
         <v>0.01</v>
@@ -4812,7 +4820,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B96" s="22" t="str">
         <f>_xll.qlHullWhite(B93,B94,B95,B93)</f>
@@ -4825,7 +4833,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B97" s="22" t="str">
         <f>_xll.qlTimeGridFromTimes(B104:B219,B96)</f>
@@ -4838,7 +4846,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B98" s="22" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine2(B96,B97,,B97)</f>
@@ -4851,7 +4859,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B99" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B92,B98,B98)</f>
@@ -4868,16 +4876,16 @@
       </c>
       <c r="B100" s="29">
         <f>_xll.qlBondCleanPrice(B92,B99)</f>
-        <v>110.79534305046033</v>
+        <v>104.56342874994053</v>
       </c>
       <c r="C100" s="30">
         <f>_xll.qlBondCleanPrice(C92,C99)</f>
-        <v>104.21047805357765</v>
+        <v>104.56342874994053</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B104" s="2">
         <v>0</v>
@@ -5541,13 +5549,13 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C8" s="79" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5556,7 +5564,7 @@
       </c>
       <c r="B9" s="78"/>
       <c r="C9" s="79" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5595,15 +5603,15 @@
         <v>126</v>
       </c>
       <c r="B13" s="80" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B14" s="80">
         <v>46754</v>
@@ -5627,7 +5635,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B16" s="86" t="str">
         <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15,B15)</f>
@@ -5848,7 +5856,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B33" s="22">
         <v>0.15</v>
@@ -5872,7 +5880,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="29" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(B33,B34)</f>
@@ -5885,7 +5893,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B36" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B16,B35)</f>
@@ -5965,11 +5973,11 @@
       </c>
       <c r="B42" s="61">
         <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual",,,B36)</f>
-        <v>2.9888064241409308E-2</v>
+        <v>2.9888059373415064E-2</v>
       </c>
       <c r="C42" s="62">
         <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual",,,C36)</f>
-        <v>2.9888064241409308E-2</v>
+        <v>2.9888059373415064E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -5991,11 +5999,11 @@
       </c>
       <c r="B44" s="48">
         <f>_xll.qlBondYield2(B16,B43,"actual360","CONTINUOUS","annual",,,,,B43)</f>
-        <v>2.9888064241409308E-2</v>
+        <v>2.9888059373415064E-2</v>
       </c>
       <c r="C44" s="49">
         <f>_xll.qlBondYield2(C16,C43,"actual360","CONTINUOUS","annual")</f>
-        <v>2.9888064241409308E-2</v>
+        <v>2.9888059373415064E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -6050,7 +6058,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B49" s="22" t="str">
         <f>_xll.qlCallableBondCallability(B16,B16)</f>
@@ -6076,7 +6084,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B51" s="22" t="str">
         <f>_xll.qlBondPrice(B37,"Clean",B37)</f>
@@ -6089,7 +6097,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B52" s="22" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B51)</f>
@@ -6102,7 +6110,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B53" s="60">
         <v>9.9999999999999995E-7</v>
@@ -6113,7 +6121,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B54" s="22">
         <v>100</v>
@@ -6124,7 +6132,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B55" s="22">
         <v>0.01</v>
@@ -6135,7 +6143,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B56" s="22">
         <v>0.5</v>
@@ -6146,33 +6154,33 @@
     </row>
     <row r="57" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B57" s="73">
         <f>_xll.qlCallableBondImpliedVolatility(B16,B51,B52,B53,B54,B55,B56,B52)</f>
-        <v>0.49070370787832679</v>
+        <v>0.49070370870006957</v>
       </c>
       <c r="C57" s="74">
         <f>_xll.qlCallableBondImpliedVolatility(C16,C51,C52,C53,C54,C55,C56)</f>
-        <v>0.49070370787832679</v>
+        <v>0.49070370870006957</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B58" s="67">
         <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual",,B36)</f>
-        <v>80.879869761049534</v>
+        <v>80.879869761049548</v>
       </c>
       <c r="C58" s="68">
         <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual",,C36)</f>
-        <v>80.879869761049534</v>
+        <v>80.879869761049548</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B59" s="67">
         <f>_xll.qlCallableBondOAS(B16,B58,B34,"30/360","compounded","Annual",,,,,B58)</f>
@@ -6185,7 +6193,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B60" s="22">
         <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
@@ -6198,7 +6206,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B61" s="67">
         <f>_xll.qlCallableBondEffectiveConvexity(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
@@ -6211,7 +6219,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B62" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B61)</f>
@@ -6224,7 +6232,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B63" s="61">
         <v>5.0000000000000001E-3</v>
@@ -6235,47 +6243,47 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B64" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B65" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C65" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B66" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C66" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B67" s="61"/>
       <c r="C67" s="62"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B68" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B16,B62,B63,B64,B65,B66,,B62)</f>
@@ -6293,7 +6301,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B70" s="19" t="str">
         <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15,B16)</f>
@@ -6306,7 +6314,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B71" s="22" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B70)</f>
@@ -6319,7 +6327,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B72" s="22">
         <v>0.03</v>
@@ -6330,7 +6338,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B73" s="22">
         <v>0.01</v>
@@ -6341,7 +6349,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B74" s="22" t="str">
         <f>_xll.qlHullWhite(B71,B72,B73,B71)</f>
@@ -6354,7 +6362,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B75" s="22">
         <v>100</v>
@@ -6365,7 +6373,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B76" s="22" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine(B74,B75,,B74)</f>
@@ -6378,7 +6386,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B77" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B70,B76)</f>
@@ -6404,7 +6412,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B79" s="19" t="str">
         <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15,B16)</f>
@@ -6417,7 +6425,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B80" s="22" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B79)</f>
@@ -6430,7 +6438,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B81" s="22">
         <v>0.03</v>
@@ -6441,7 +6449,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B82" s="22">
         <v>0.01</v>
@@ -6452,7 +6460,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B83" s="22" t="str">
         <f>_xll.qlHullWhite(B80,B81,B82,B80)</f>
@@ -6465,7 +6473,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B84" s="22" t="str">
         <f>_xll.qlTimeGridFromTimes(B91:B206,B83)</f>
@@ -6478,7 +6486,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B85" s="22" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine2(B83,B84,,B84)</f>
@@ -6491,7 +6499,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B86" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B79,B85)</f>
@@ -6508,16 +6516,16 @@
       </c>
       <c r="B87" s="29">
         <f>_xll.qlBondCleanPrice(B79,B86)</f>
-        <v>86.905812107181106</v>
+        <v>86.905812980554899</v>
       </c>
       <c r="C87" s="30">
         <f>_xll.qlBondCleanPrice(C79,C86)</f>
-        <v>86.905812107181106</v>
+        <v>86.905812980554899</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B91" s="2">
         <v>0</v>
@@ -7154,7 +7162,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B6" s="22" t="b">
         <v>0</v>
@@ -7165,7 +7173,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B7" s="22">
         <v>100</v>
@@ -7176,7 +7184,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>76</v>
@@ -7187,18 +7195,18 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B10" s="22" t="str">
         <f>_xll.qlCustomRegion("TestRegion","TR",B2)</f>
@@ -7211,7 +7219,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B11" s="22" t="b">
         <v>0</v>
@@ -7222,18 +7230,18 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>76</v>
@@ -7255,7 +7263,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B15" s="39">
         <v>45293</v>
@@ -7266,7 +7274,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B16" s="41">
         <v>47485</v>
@@ -7277,7 +7285,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" s="22">
         <v>0.02</v>
@@ -7288,7 +7296,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18" s="22">
         <v>0.02</v>
@@ -7299,7 +7307,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="90" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B19" s="29" t="str">
         <f>_xll.qlZeroInflationCurve($B$1,B15:B16,B17:B18,"Annual","Actual365fixed",,B10)</f>
@@ -7312,7 +7320,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B20" s="29" t="str">
         <f>_xll.qlZeroInflationIndex(B9,B10,B11,B12,B13,B14,B19,B19)</f>
@@ -7336,7 +7344,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B22" s="22">
         <v>100</v>
@@ -7347,7 +7355,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="90" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B23" s="29" t="b">
         <f>_xll.qlIndexAddFixing(B20,B21,B22,TRUE,B20)</f>
@@ -7360,13 +7368,13 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -7396,10 +7404,10 @@
         <v>46</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -7407,10 +7415,10 @@
         <v>60</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -7440,10 +7448,10 @@
         <v>77</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -7486,10 +7494,10 @@
         <v>83</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -7520,7 +7528,7 @@
       </c>
       <c r="B38" s="22"/>
       <c r="C38" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -7538,7 +7546,7 @@
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -7561,7 +7569,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B43" s="30" t="str">
         <f>_xll.qlCPIBond(B4,B5,B6,B7,B8,B20,B24,B33,B34,B35,B36,B37,,,,,,B33)</f>
@@ -7795,7 +7803,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B61" s="22" t="str">
         <f>_xll.qlDiscountingBondEngine(B60,B60)</f>
@@ -7808,7 +7816,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B62" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B43,B61,B61)</f>
@@ -7888,11 +7896,11 @@
       </c>
       <c r="B68" s="61">
         <f>_xll.qlBondYield(B43,"actual360","CONTINUOUS","annual",,,B62)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544384E-2</v>
       </c>
       <c r="C68" s="62">
         <f>_xll.qlBondYield(C43,"actual360","CONTINUOUS","annual",,,C62)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544384E-2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -7914,11 +7922,11 @@
       </c>
       <c r="B70" s="48">
         <f>_xll.qlBondYield2(B43,B69,"actual360","CONTINUOUS","annual",,,,,B69)</f>
-        <v>3.0038936376571658E-2</v>
+        <v>2.9558802241544384E-2</v>
       </c>
       <c r="C70" s="49">
         <f>_xll.qlBondYield2(C43,C69,"actual360","CONTINUOUS","annual",,,,,C69)</f>
-        <v>3.0038936376571658E-2</v>
+        <v>2.9558802241544384E-2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -7973,7 +7981,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B75" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B43)</f>
@@ -7986,7 +7994,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B76" s="61">
         <v>5.0000000000000001E-3</v>
@@ -7997,47 +8005,47 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B77" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C77" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B78" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C78" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B79" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C79" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B80" s="61"/>
       <c r="C80" s="62"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B81" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B43,B75,B76,B77,B78,B79,,B75)</f>
@@ -8149,7 +8157,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B4" s="40">
         <v>45659</v>
@@ -8157,18 +8165,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>202</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -8176,12 +8184,12 @@
         <v>68</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="43" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B8" s="30" t="str">
         <f>_xll.qlBondSinkingSchedule(B4,B5,B6,B7)</f>
@@ -8190,23 +8198,23 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B12" s="23">
         <v>0.05</v>
@@ -8214,7 +8222,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B13" s="23">
         <v>1000000</v>
@@ -8222,7 +8230,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="93" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B14" s="23">
         <f>_xll.qlBondSinkingNotionals(B10,B11,B12,B13)</f>
@@ -8231,10 +8239,10 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="99" t="s">
         <v>207</v>
-      </c>
-      <c r="B15" s="99" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -8325,7 +8333,7 @@
         <v>48</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C9" s="37"/>
     </row>
@@ -8703,7 +8711,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B43" s="22" t="str">
         <f>_xll.qlDiscountingBondEngine(B42,B42)</f>
@@ -8716,7 +8724,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B44" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B25,B43,B43)</f>
@@ -8796,11 +8804,11 @@
       </c>
       <c r="B50" s="61">
         <f>_xll.qlBondYield(B25,"actual360","CONTINUOUS","annual",,,B44)</f>
-        <v>2.9558799531199026E-2</v>
+        <v>2.9558802241544502E-2</v>
       </c>
       <c r="C50" s="62">
         <f>_xll.qlBondYield(C25,"actual360","CONTINUOUS","annual",,,C44)</f>
-        <v>2.9558799531199026E-2</v>
+        <v>2.9558802241544502E-2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -8822,11 +8830,11 @@
       </c>
       <c r="B52" s="48">
         <f>_xll.qlBondYield2(B25,B51,"actual360","CONTINUOUS","annual",,,,,B51)</f>
-        <v>2.9558799531199026E-2</v>
+        <v>2.9558802241544502E-2</v>
       </c>
       <c r="C52" s="49">
         <f>_xll.qlBondYield2(C25,C51,"actual360","CONTINUOUS","annual",,,,,C51)</f>
-        <v>2.9558799531199026E-2</v>
+        <v>2.9558802241544502E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -9221,7 +9229,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B29" s="29" t="str">
         <f>_xll.qlDiscountingBondEngine(B28,B28)</f>
@@ -9234,7 +9242,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B30" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B11,B29,B29)</f>
@@ -9314,11 +9322,11 @@
       </c>
       <c r="B36" s="61">
         <f>_xll.qlBondYield(B11,"actual360","CONTINUOUS","annual",,,B30)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544429E-2</v>
       </c>
       <c r="C36" s="62">
         <f>_xll.qlBondYield(C11,"actual360","CONTINUOUS","annual",,,C30)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544405E-2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -9340,11 +9348,11 @@
       </c>
       <c r="B38" s="48">
         <f>_xll.qlBondYield2(B11,B37,"actual360","CONTINUOUS","annual",,,,,B37)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544429E-2</v>
       </c>
       <c r="C38" s="49">
         <f>_xll.qlBondYield2(C11,C37,"actual360","CONTINUOUS","annual",,,,,C30)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544405E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -9399,7 +9407,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B11)</f>
@@ -9412,7 +9420,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="61">
         <v>5.0000000000000001E-3</v>
@@ -9423,47 +9431,47 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C45" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C46" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B47" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C47" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B48" s="61"/>
       <c r="C48" s="62"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B49" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B11,B43,B44,B45,B46,B47,,B43)</f>
@@ -9664,10 +9672,10 @@
         <v>67</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -9980,7 +9988,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B45" s="22" t="str">
         <f>_xll.qlDiscountingBondEngine(B44,B44)</f>
@@ -9993,7 +10001,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B46" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B27,B45,B45)</f>
@@ -10073,11 +10081,11 @@
       </c>
       <c r="B52" s="61">
         <f>_xll.qlBondYield(B27,"actual360","CONTINUOUS","annual",,,B46)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544439E-2</v>
       </c>
       <c r="C52" s="62">
         <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual",,,C46)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544429E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -10099,11 +10107,11 @@
       </c>
       <c r="B54" s="48">
         <f>_xll.qlBondYield2(B27,B53,"actual360","CONTINUOUS","annual",,,,,B53)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544439E-2</v>
       </c>
       <c r="C54" s="49">
         <f>_xll.qlBondYield2(C27,C53,"actual360","CONTINUOUS","annual",,,,,C53)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544429E-2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -10158,7 +10166,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B59" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B27)</f>
@@ -10171,7 +10179,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B60" s="61">
         <v>5.0000000000000001E-3</v>
@@ -10182,47 +10190,47 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B61" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C61" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B62" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C62" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B63" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C63" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B64" s="61"/>
       <c r="C64" s="62"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B65" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B27,B59,B60,B61,B62,B63,,B59)</f>
@@ -10441,10 +10449,10 @@
         <v>83</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -10761,7 +10769,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B48" s="22" t="str">
         <f>_xll.qlDiscountingBondEngine(B47,B47)</f>
@@ -10774,7 +10782,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="89" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B49" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B30,B48,B48)</f>
@@ -10854,11 +10862,11 @@
       </c>
       <c r="B55" s="61">
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual",,,B49)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544418E-2</v>
       </c>
       <c r="C55" s="62">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual",,,C49)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544401E-2</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -10880,11 +10888,11 @@
       </c>
       <c r="B57" s="48">
         <f>_xll.qlBondYield2(B30,B56,"actual360","CONTINUOUS","annual",,,,,B56)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544418E-2</v>
       </c>
       <c r="C57" s="49">
         <f>_xll.qlBondYield2(C30,C56,"actual360","CONTINUOUS","annual",,,,,C56)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544401E-2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -10939,7 +10947,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B62" s="61" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B30)</f>
@@ -10952,7 +10960,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B63" s="61">
         <v>5.0000000000000001E-3</v>
@@ -10963,47 +10971,47 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B64" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B65" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C65" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B66" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C66" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B67" s="61"/>
       <c r="C67" s="62"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B68" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B30,B62,B63,B64,B65,B66,,B62)</f>
@@ -11223,10 +11231,10 @@
         <v>83</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -11588,7 +11596,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B52" s="22" t="str">
         <f>_xll.qlDiscountingBondEngine(B51,B51)</f>
@@ -11601,7 +11609,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="89" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B53" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B34,B52,B52)</f>
@@ -11681,11 +11689,11 @@
       </c>
       <c r="B59" s="61">
         <f>_xll.qlBondYield(B34,"actual360","CONTINUOUS","annual",,,B53)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544439E-2</v>
       </c>
       <c r="C59" s="62">
         <f>_xll.qlBondYield(C34,"actual360","CONTINUOUS","annual",,,C53)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544436E-2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -11707,11 +11715,11 @@
       </c>
       <c r="B61" s="48">
         <f>_xll.qlBondYield2(B34,B60,"actual360","CONTINUOUS","annual",,,,,B60)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544439E-2</v>
       </c>
       <c r="C61" s="49">
         <f>_xll.qlBondYield2(C34,C60,"actual360","CONTINUOUS","annual",,,,,C60)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544436E-2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -11766,7 +11774,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B66" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B34)</f>
@@ -11779,7 +11787,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B67" s="61">
         <v>5.0000000000000001E-3</v>
@@ -11790,47 +11798,47 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B68" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C68" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B69" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C69" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C70" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B71" s="61"/>
       <c r="C71" s="62"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B72" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B34,B66,B67,B68,B69,B70,,B53)</f>
@@ -12032,10 +12040,10 @@
         <v>67</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -12154,11 +12162,11 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -12397,7 +12405,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B50" s="22" t="str">
         <f>_xll.qlDiscountingBondEngine(B49,B49)</f>
@@ -12410,7 +12418,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="89" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B51" s="22" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B32,B50,B50)</f>
@@ -12490,11 +12498,11 @@
       </c>
       <c r="B57" s="61">
         <f>_xll.qlBondYield(B32,"actual360","CONTINUOUS","annual",,,B51)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544408E-2</v>
       </c>
       <c r="C57" s="62">
         <f>_xll.qlBondYield(C32,"actual360","CONTINUOUS","annual",,,C51)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544408E-2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -12516,11 +12524,11 @@
       </c>
       <c r="B59" s="48">
         <f>_xll.qlBondYield2(B32,B58,"actual360","CONTINUOUS","annual",,,,,B58)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544408E-2</v>
       </c>
       <c r="C59" s="49">
         <f>_xll.qlBondYield2(C32,C58,"actual360","CONTINUOUS","annual",,,,,C58)</f>
-        <v>2.9558808088302614E-2</v>
+        <v>2.9558802241544408E-2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -12575,7 +12583,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B64" s="46" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed",,,B32)</f>
@@ -12588,7 +12596,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B65" s="61">
         <v>5.0000000000000001E-3</v>
@@ -12599,47 +12607,47 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B66" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C66" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B67" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C67" s="62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B68" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C68" s="62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B69" s="61"/>
       <c r="C69" s="62"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B70" s="29">
         <f>_xll.qlBondCleanPriceFromZSpread(B32,B64,B65,B66,B67,B68,,B64)</f>
